--- a/exports/SHRIRAMFIN_full_report.xlsx
+++ b/exports/SHRIRAMFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>241</v>
+        <v>237.2</v>
       </c>
       <c r="I2" t="n">
         <v>238.0770127480409</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.19</v>
+        <v>-2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="M2" t="n">
         <v>0.44</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.79</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>246.85</v>
+        <v>253.45</v>
       </c>
       <c r="I3" t="n">
         <v>251.8113758054948</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.07</v>
+        <v>-6.85</v>
       </c>
       <c r="L3" t="n">
-        <v>5.19</v>
+        <v>9.59</v>
       </c>
       <c r="M3" t="n">
-        <v>0.43</v>
+        <v>1.28</v>
       </c>
       <c r="N3" t="n">
         <v>5.04</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>9.18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>237.6</v>
+        <v>231.2</v>
       </c>
       <c r="I4" t="n">
         <v>236.8738796761089</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.25</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.73</v>
+        <v>8.98</v>
       </c>
       <c r="M4" t="n">
         <v>1.95</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44608.55208333334</v>
+        <v>44609.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>243.8</v>
+        <v>255</v>
       </c>
       <c r="I5" t="n">
         <v>253.150867544505</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.45</v>
+        <v>-10.29</v>
       </c>
       <c r="L5" t="n">
-        <v>10.21</v>
+        <v>10.92</v>
       </c>
       <c r="M5" t="n">
         <v>1.32</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.92</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>236.15</v>
+        <v>220.95</v>
       </c>
       <c r="I6" t="n">
         <v>233.0448377736527</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.39</v>
+        <v>-13.35</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>14.41</v>
       </c>
       <c r="M6" t="n">
-        <v>0.83</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>3.51</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>4.39</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.41</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>221.2</v>
+        <v>226.75</v>
       </c>
       <c r="I7" t="n">
         <v>225.5166072500887</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.11</v>
+        <v>-2.63</v>
       </c>
       <c r="L7" t="n">
         <v>4.96</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.49</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44669.55208333334</v>
+        <v>44670.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>233</v>
+        <v>227.8</v>
       </c>
       <c r="I8" t="n">
         <v>230.7975582067213</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K8" t="n">
-        <v>2.76</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>5.98</v>
@@ -897,7 +992,7 @@
         <v>1.78</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="O8" t="n">
         <v>1.81</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>9.75</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>229.5</v>
+        <v>243.05</v>
       </c>
       <c r="I9" t="n">
         <v>235.6091026541111</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.75</v>
+        <v>-6.69</v>
       </c>
       <c r="L9" t="n">
-        <v>4.39</v>
+        <v>8.69</v>
       </c>
       <c r="M9" t="n">
-        <v>1.22</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
         <v>4.89</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44691.55208333334</v>
+        <v>44692.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>231.4</v>
+        <v>222.8</v>
       </c>
       <c r="I10" t="n">
         <v>225.7000583944539</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.79</v>
+        <v>-8.33</v>
       </c>
       <c r="L10" t="n">
-        <v>6.85</v>
+        <v>9.69</v>
       </c>
       <c r="M10" t="n">
         <v>3.57</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>231.2</v>
+        <v>236.6</v>
       </c>
       <c r="I11" t="n">
         <v>235.4508218562094</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.77</v>
+        <v>-6.19</v>
       </c>
       <c r="L11" t="n">
-        <v>4.49</v>
+        <v>6.37</v>
       </c>
       <c r="M11" t="n">
         <v>2.15</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>292.2</v>
+        <v>275.85</v>
       </c>
       <c r="I12" t="n">
         <v>281.5544355133016</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>23.5</v>
+        <v>16.59</v>
       </c>
       <c r="L12" t="n">
         <v>5.96</v>
@@ -1125,7 +1268,7 @@
         <v>1.72</v>
       </c>
       <c r="N12" t="n">
-        <v>2.67</v>
+        <v>5.41</v>
       </c>
       <c r="O12" t="n">
         <v>3.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44810.38541666666</v>
+        <v>44810.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>274.3</v>
+        <v>277</v>
       </c>
       <c r="I13" t="n">
         <v>275.5333826526524</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="L13" t="n">
         <v>7.3</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.71</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>265.05</v>
+        <v>257.4</v>
       </c>
       <c r="I14" t="n">
         <v>261.1718451415947</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.31</v>
+        <v>-7.08</v>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>7.17</v>
       </c>
       <c r="M14" t="n">
         <v>0.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="O14" t="n">
         <v>4.84</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44861.38541666666</v>
+        <v>44861.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>248.7</v>
+        <v>250.6</v>
       </c>
       <c r="I15" t="n">
         <v>249.8116742952145</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="L15" t="n">
         <v>3.96</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.26</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44893.38541666666</v>
+        <v>44893.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>255.35</v>
+        <v>249.6</v>
       </c>
       <c r="I16" t="n">
         <v>251.6623902247013</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="L16" t="n">
         <v>4.55</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.76</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>257</v>
+        <v>271.8</v>
       </c>
       <c r="I17" t="n">
         <v>270.0299440662124</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.96</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>3.75</v>
+        <v>10.14</v>
       </c>
       <c r="M17" t="n">
         <v>0.38</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>266.4</v>
+        <v>260.25</v>
       </c>
       <c r="I18" t="n">
         <v>262.6977508290159</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.99</v>
+        <v>-4.25</v>
       </c>
       <c r="L18" t="n">
         <v>6.7</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>8.41</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>249.7</v>
+        <v>267.2</v>
       </c>
       <c r="I19" t="n">
         <v>261.51730689895</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>4.05</v>
+        <v>-2.67</v>
       </c>
       <c r="L19" t="n">
         <v>7.36</v>
       </c>
       <c r="M19" t="n">
-        <v>1.14</v>
+        <v>6.37</v>
       </c>
       <c r="N19" t="n">
         <v>4.96</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.49</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44973.55208333334</v>
+        <v>44974.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>250.65</v>
+        <v>247.4</v>
       </c>
       <c r="I20" t="n">
         <v>248.6313801351679</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.19</v>
+        <v>-7.41</v>
       </c>
       <c r="L20" t="n">
-        <v>6.68</v>
+        <v>7.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.25</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.26</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>248.6</v>
+        <v>253.8</v>
       </c>
       <c r="I21" t="n">
         <v>251.3860761406557</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.49</v>
+        <v>-2.59</v>
       </c>
       <c r="L21" t="n">
-        <v>1.96</v>
+        <v>4.69</v>
       </c>
       <c r="M21" t="n">
         <v>2.21</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.71</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>249.2</v>
+        <v>243.2</v>
       </c>
       <c r="I22" t="n">
         <v>244.5603556093782</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.81</v>
+        <v>-4.18</v>
       </c>
       <c r="L22" t="n">
-        <v>3.76</v>
+        <v>4.61</v>
       </c>
       <c r="M22" t="n">
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
         <v>2.23</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>254.85</v>
+        <v>257.6</v>
       </c>
       <c r="I23" t="n">
         <v>255.375062930075</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.79</v>
+        <v>-5.92</v>
       </c>
       <c r="L23" t="n">
-        <v>5.43</v>
+        <v>6.17</v>
       </c>
       <c r="M23" t="n">
         <v>2.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>281</v>
+        <v>264.9</v>
       </c>
       <c r="I24" t="n">
         <v>271.2878727325789</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>9.08</v>
+        <v>2.83</v>
       </c>
       <c r="L24" t="n">
         <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0.54</v>
+        <v>3.91</v>
       </c>
       <c r="N24" t="n">
-        <v>1.87</v>
+        <v>5.14</v>
       </c>
       <c r="O24" t="n">
         <v>2.2</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>276.4</v>
+        <v>280.95</v>
       </c>
       <c r="I25" t="n">
         <v>276.4579474763876</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.34</v>
+        <v>-6.06</v>
       </c>
       <c r="L25" t="n">
-        <v>5.7</v>
+        <v>7.47</v>
       </c>
       <c r="M25" t="n">
         <v>1.22</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>376.6</v>
+        <v>372.45</v>
       </c>
       <c r="I26" t="n">
         <v>375.0007061540866</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>122</v>
+        <v>122.1666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>34.05</v>
+        <v>32.57</v>
       </c>
       <c r="L26" t="n">
         <v>1.51</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.65</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>359.95</v>
+        <v>386.7</v>
       </c>
       <c r="I27" t="n">
         <v>379.7789187492237</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>3.36</v>
+        <v>-3.83</v>
       </c>
       <c r="L27" t="n">
-        <v>4.18</v>
+        <v>8.99</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>7.71</v>
       </c>
       <c r="O27" t="n">
         <v>-1.6</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.41</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45254.38541666666</v>
+        <v>45254.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>391.15</v>
+        <v>388.25</v>
       </c>
       <c r="I28" t="n">
         <v>388.9081660161527</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="L28" t="n">
         <v>4.27</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.74</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>399.45</v>
+        <v>409.7</v>
       </c>
       <c r="I29" t="n">
         <v>406.0324829618019</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.88</v>
+        <v>-5.52</v>
       </c>
       <c r="L29" t="n">
-        <v>4.57</v>
+        <v>7.55</v>
       </c>
       <c r="M29" t="n">
-        <v>0.62</v>
+        <v>1.39</v>
       </c>
       <c r="N29" t="n">
-        <v>1.44</v>
+        <v>5.09</v>
       </c>
       <c r="O29" t="n">
         <v>-1.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.84</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>416.7</v>
+        <v>398.8</v>
       </c>
       <c r="I30" t="n">
         <v>399.5895631855332</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.71</v>
+        <v>-2.66</v>
       </c>
       <c r="L30" t="n">
         <v>3.54</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>417.6</v>
+        <v>428.45</v>
       </c>
       <c r="I31" t="n">
         <v>422.982256046547</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.71</v>
+        <v>-7.43</v>
       </c>
       <c r="L31" t="n">
-        <v>5.22</v>
+        <v>7.95</v>
       </c>
       <c r="M31" t="n">
         <v>0.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="O31" t="n">
         <v>-3.11</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.79</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>467.4</v>
+        <v>456.15</v>
       </c>
       <c r="I32" t="n">
         <v>462.1148321412791</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>9.09</v>
+        <v>6.47</v>
       </c>
       <c r="L32" t="n">
         <v>2.43</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>7.99</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>480.6</v>
+        <v>487.4</v>
       </c>
       <c r="I33" t="n">
         <v>483.4191442235896</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.36</v>
+        <v>-6.85</v>
       </c>
       <c r="L33" t="n">
-        <v>5.43</v>
+        <v>8.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04</v>
+        <v>1.43</v>
       </c>
       <c r="N33" t="n">
         <v>3</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.86</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45350.38541666666</v>
+        <v>45350.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>477.5</v>
+        <v>468</v>
       </c>
       <c r="I34" t="n">
         <v>470.3108341538882</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.03</v>
+        <v>-3.98</v>
       </c>
       <c r="L34" t="n">
         <v>7.39</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.99</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>483.1</v>
+        <v>487.4</v>
       </c>
       <c r="I35" t="n">
         <v>487.1230242223993</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.23</v>
+        <v>-4.15</v>
       </c>
       <c r="L35" t="n">
         <v>6.84</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.09</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>497.2</v>
+        <v>485.25</v>
       </c>
       <c r="I36" t="n">
         <v>488.0360019856942</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>2.01</v>
+        <v>-0.44</v>
       </c>
       <c r="L36" t="n">
         <v>0.88</v>
@@ -2493,7 +2924,7 @@
         <v>0.29</v>
       </c>
       <c r="N36" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="O36" t="n">
         <v>2.96</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.68</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="I37" t="n">
         <v>496.8597218502143</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.39</v>
+        <v>-2.63</v>
       </c>
       <c r="L37" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M37" t="n">
         <v>0.8</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.8</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>489.8</v>
+        <v>483.35</v>
       </c>
       <c r="I38" t="n">
         <v>484.8848507970679</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.65</v>
+        <v>-2.94</v>
       </c>
       <c r="L38" t="n">
         <v>6.14</v>
@@ -2607,7 +3062,7 @@
         <v>0.22</v>
       </c>
       <c r="N38" t="n">
-        <v>2.01</v>
+        <v>3.46</v>
       </c>
       <c r="O38" t="n">
         <v>0.15</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>477</v>
+        <v>504.2</v>
       </c>
       <c r="I39" t="n">
         <v>486.6906467590009</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>1.31</v>
+        <v>-4.31</v>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>5.39</v>
       </c>
       <c r="M39" t="n">
-        <v>1.45</v>
+        <v>2.73</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>5.53</v>
       </c>
       <c r="O39" t="n">
         <v>-3.46</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>8.26</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>503.4</v>
+        <v>455.65</v>
       </c>
       <c r="I40" t="n">
         <v>470.1448891614195</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.16</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>3.8</v>
+        <v>13.01</v>
       </c>
       <c r="M40" t="n">
         <v>-0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>9.42</v>
       </c>
       <c r="O40" t="n">
         <v>5.53</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45453.55208333334</v>
+        <v>45454.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>501.6</v>
+        <v>508.9</v>
       </c>
       <c r="I41" t="n">
         <v>507.7456397792502</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.08</v>
+        <v>-11.69</v>
       </c>
       <c r="L41" t="n">
         <v>12.04</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>571.05</v>
+        <v>563</v>
       </c>
       <c r="I42" t="n">
         <v>563.772811856726</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K42" t="n">
-        <v>12.21</v>
+        <v>10.63</v>
       </c>
       <c r="L42" t="n">
         <v>2.14</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>5.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45499.38541666666</v>
+        <v>45499.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>553</v>
+        <v>586.4</v>
       </c>
       <c r="I43" t="n">
         <v>573.5380662914167</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>1.78</v>
+        <v>-4.16</v>
       </c>
       <c r="L43" t="n">
-        <v>3.02</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>1.04</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.33</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>713.6</v>
+        <v>686.6</v>
       </c>
       <c r="I44" t="n">
         <v>690.6157281365813</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>67</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>21.69</v>
+        <v>17.09</v>
       </c>
       <c r="L44" t="n">
         <v>7.13</v>
@@ -2949,7 +3476,7 @@
         <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>3.52</v>
+        <v>4.36</v>
       </c>
       <c r="O44" t="n">
         <v>9.48</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.52</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>591.55</v>
+        <v>601</v>
       </c>
       <c r="I45" t="n">
         <v>596.1779616079497</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K45" t="n">
-        <v>13.84</v>
+        <v>12.47</v>
       </c>
       <c r="L45" t="n">
         <v>4.14</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.71</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>626</v>
+        <v>601.6</v>
       </c>
       <c r="I46" t="n">
         <v>618.4042590164563</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>4.16</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="n">
         <v>1.86</v>
@@ -3063,7 +3614,7 @@
         <v>0.75</v>
       </c>
       <c r="N46" t="n">
-        <v>2.43</v>
+        <v>5.05</v>
       </c>
       <c r="O46" t="n">
         <v>2.92</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>584.1</v>
+        <v>608.4</v>
       </c>
       <c r="I47" t="n">
         <v>606.3630499899519</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>2.91</v>
+        <v>-1.13</v>
       </c>
       <c r="L47" t="n">
         <v>4.22</v>
@@ -3120,7 +3683,7 @@
         <v>0.96</v>
       </c>
       <c r="N47" t="n">
-        <v>1.67</v>
+        <v>4.47</v>
       </c>
       <c r="O47" t="n">
         <v>-5.05</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.89</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>590.8</v>
+        <v>571.3</v>
       </c>
       <c r="I48" t="n">
         <v>582.28244815029</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.89</v>
+        <v>-6.1</v>
       </c>
       <c r="L48" t="n">
-        <v>3.63</v>
+        <v>6.62</v>
       </c>
       <c r="M48" t="n">
         <v>0.79</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.18</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45691.55208333334</v>
+        <v>45692.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>548.05</v>
+        <v>570</v>
       </c>
       <c r="I49" t="n">
         <v>553.5209864636789</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K49" t="n">
-        <v>4.07</v>
+        <v>0.23</v>
       </c>
       <c r="L49" t="n">
         <v>3.97</v>
@@ -3234,7 +3821,7 @@
         <v>1.88</v>
       </c>
       <c r="N49" t="n">
-        <v>5.16</v>
+        <v>5.28</v>
       </c>
       <c r="O49" t="n">
         <v>-1.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.83</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>643.3</v>
+        <v>637.85</v>
       </c>
       <c r="I50" t="n">
         <v>642.78247654856</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>12.86</v>
+        <v>11.9</v>
       </c>
       <c r="L50" t="n">
         <v>7.88</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.22</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>637.5</v>
+        <v>670.65</v>
       </c>
       <c r="I51" t="n">
         <v>666.5653063505578</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>0.05</v>
+        <v>-5.14</v>
       </c>
       <c r="L51" t="n">
-        <v>4.26</v>
+        <v>5.32</v>
       </c>
       <c r="M51" t="n">
-        <v>0.76</v>
+        <v>2.27</v>
       </c>
       <c r="N51" t="n">
-        <v>4.35</v>
+        <v>5.39</v>
       </c>
       <c r="O51" t="n">
         <v>-2.8</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>10.66</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>675.15</v>
+        <v>638.05</v>
       </c>
       <c r="I52" t="n">
         <v>655.3681588926415</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.67</v>
+        <v>-4.86</v>
       </c>
       <c r="L52" t="n">
-        <v>3.21</v>
+        <v>5.32</v>
       </c>
       <c r="M52" t="n">
         <v>0.01</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.71</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>641.3</v>
+        <v>644.5</v>
       </c>
       <c r="I53" t="n">
         <v>643.0050786320828</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.51</v>
+        <v>-1.01</v>
       </c>
       <c r="L53" t="n">
         <v>6.98</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.59</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>660.75</v>
+        <v>654.9</v>
       </c>
       <c r="I54" t="n">
         <v>657.637429247716</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>2.52</v>
+        <v>1.61</v>
       </c>
       <c r="L54" t="n">
         <v>3.03</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>687.2</v>
+        <v>699.95</v>
       </c>
       <c r="I55" t="n">
         <v>688.9652241065181</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.93</v>
+        <v>-6.88</v>
       </c>
       <c r="L55" t="n">
-        <v>5.26</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>1.61</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.64</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>675.2</v>
+        <v>673.4</v>
       </c>
       <c r="I56" t="n">
         <v>674.6758867386325</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.54</v>
+        <v>-3.79</v>
       </c>
       <c r="L56" t="n">
-        <v>3.86</v>
+        <v>4.28</v>
       </c>
       <c r="M56" t="n">
         <v>0.07000000000000001</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.41</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45910.38541666666</v>
+        <v>45910.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>602.1</v>
+        <v>605.7</v>
       </c>
       <c r="I57" t="n">
         <v>603.7791423842998</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>10.59</v>
+        <v>10.05</v>
       </c>
       <c r="L57" t="n">
         <v>2.17</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.49</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="I58" t="n">
         <v>609.2919674597199</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>1.04</v>
+        <v>0.05</v>
       </c>
       <c r="L58" t="n">
         <v>0.78</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>617.85</v>
+        <v>646</v>
       </c>
       <c r="I59" t="n">
         <v>633.2809785981832</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.96</v>
+        <v>-6.6</v>
       </c>
       <c r="L59" t="n">
-        <v>2.43</v>
+        <v>6.72</v>
       </c>
       <c r="M59" t="n">
         <v>0.48</v>
       </c>
       <c r="N59" t="n">
-        <v>1.36</v>
+        <v>4.77</v>
       </c>
       <c r="O59" t="n">
         <v>-1.03</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.12</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45994.38541666666</v>
+        <v>45994.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>835.25</v>
+        <v>828</v>
       </c>
       <c r="I60" t="n">
         <v>832.3741666098867</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>29.3</v>
+        <v>28.17</v>
       </c>
       <c r="L60" t="n">
         <v>4.64</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.82</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46008.38541666666</v>
+        <v>46008.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I61" t="n">
         <v>864.4555580136797</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.62</v>
+        <v>-4.59</v>
       </c>
       <c r="L61" t="n">
         <v>5.73</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.46</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>994</v>
+        <v>945</v>
       </c>
       <c r="I62" t="n">
         <v>967.460920867714</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>14.78</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>1.79</v>
@@ -3975,7 +4718,7 @@
         <v>0.49</v>
       </c>
       <c r="N62" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="O62" t="n">
         <v>2.47</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>10.16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1001</v>
+        <v>1042.8</v>
       </c>
       <c r="I63" t="n">
         <v>1029.418306383317</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.93</v>
+        <v>-10.35</v>
       </c>
       <c r="L63" t="n">
-        <v>10.21</v>
+        <v>10.78</v>
       </c>
       <c r="M63" t="n">
         <v>4.87</v>
       </c>
       <c r="N63" t="n">
-        <v>3.52</v>
+        <v>6.19</v>
       </c>
       <c r="O63" t="n">
         <v>-2.82</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1048.1</v>
+        <v>1009.2</v>
       </c>
       <c r="I64" t="n">
         <v>1041.175938435438</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K64" t="n">
-        <v>0.51</v>
+        <v>-3.22</v>
       </c>
       <c r="L64" t="n">
-        <v>3.78</v>
+        <v>5.31</v>
       </c>
       <c r="M64" t="n">
         <v>3.29</v>
       </c>
       <c r="N64" t="n">
-        <v>2.91</v>
+        <v>3.64</v>
       </c>
       <c r="O64" t="n">
         <v>6.19</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46090.55208333334</v>
+        <v>46091.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>989.9</v>
+        <v>1055.7</v>
       </c>
       <c r="I65" t="n">
         <v>1052.435848909462</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>1.91</v>
+        <v>-4.61</v>
       </c>
       <c r="L65" t="n">
-        <v>4.24</v>
+        <v>4.74</v>
       </c>
       <c r="M65" t="n">
-        <v>1.22</v>
+        <v>2.03</v>
       </c>
       <c r="N65" t="n">
-        <v>2.92</v>
+        <v>7.76</v>
       </c>
       <c r="O65" t="n">
         <v>-3.64</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.7</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46099.55208333334</v>
+        <v>46100.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1017.1</v>
+        <v>956.7</v>
       </c>
       <c r="I66" t="n">
         <v>966.6298161450026</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.66</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>8.18</v>
+        <v>9.4</v>
       </c>
       <c r="M66" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="N66" t="n">
-        <v>2.69</v>
+        <v>6.3</v>
       </c>
       <c r="O66" t="n">
         <v>7.76</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>11.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>930</v>
+        <v>1030.45</v>
       </c>
       <c r="I67" t="n">
         <v>961.2861479522672</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>2.79</v>
+        <v>-7.71</v>
       </c>
       <c r="L67" t="n">
-        <v>4.53</v>
+        <v>8.23</v>
       </c>
       <c r="M67" t="n">
         <v>5.45</v>
       </c>
       <c r="N67" t="n">
-        <v>5.21</v>
+        <v>10.24</v>
       </c>
       <c r="O67" t="n">
         <v>-6.3</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>12.35</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46136.55208333334</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1016</v>
+        <v>970.6</v>
       </c>
       <c r="I68" t="n">
         <v>989.011853389468</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.4</v>
+        <v>-5.81</v>
       </c>
       <c r="L68" t="n">
-        <v>5.38</v>
+        <v>6.47</v>
       </c>
       <c r="M68" t="n">
         <v>2.66</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>4.13</v>
       </c>
       <c r="O68" t="n">
         <v>10.24</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.82</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46148.38541666666</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>980.5</v>
+        <v>1006.65</v>
       </c>
       <c r="I69" t="n">
         <v>1001.496468057631</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.02</v>
+        <v>-3.71</v>
       </c>
       <c r="L69" t="n">
         <v>4.27</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>7.75</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>977</v>
+        <v>943.1</v>
       </c>
       <c r="I70" t="n">
         <v>955.6724707713776</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.95</v>
+        <v>-6.31</v>
       </c>
       <c r="L70" t="n">
-        <v>3.6</v>
+        <v>6.46</v>
       </c>
       <c r="M70" t="n">
         <v>1.3</v>
       </c>
       <c r="N70" t="n">
-        <v>2.6</v>
+        <v>4.41</v>
       </c>
       <c r="O70" t="n">
         <v>4.32</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.56</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>912.4</v>
+        <v>958</v>
       </c>
       <c r="I71" t="n">
         <v>932.8521346700588</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>3.26</v>
+        <v>-1.58</v>
       </c>
       <c r="L71" t="n">
         <v>3.91</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1044.8</v>
+        <v>1014.9</v>
       </c>
       <c r="I72" t="n">
         <v>1026.659911514237</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K72" t="n">
-        <v>9.06</v>
+        <v>5.94</v>
       </c>
       <c r="L72" t="n">
         <v>4.8</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.15</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1046.4</v>
+        <v>1084.1</v>
       </c>
       <c r="I73" t="n">
         <v>1071.303677158841</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.1</v>
+        <v>-6.82</v>
       </c>
       <c r="L73" t="n">
-        <v>6.32</v>
+        <v>7.89</v>
       </c>
       <c r="M73" t="n">
         <v>1.57</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.21</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1088.8</v>
+        <v>1078.9</v>
       </c>
       <c r="I74" t="n">
         <v>1086.884989471198</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K74" t="n">
-        <v>0.43</v>
+        <v>-0.48</v>
       </c>
       <c r="L74" t="n">
         <v>3</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>4.27</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>931.4</v>
+        <v>986.2</v>
       </c>
       <c r="I75" t="n">
         <v>973.8379944321861</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>13.67</v>
+        <v>8.59</v>
       </c>
       <c r="L75" t="n">
         <v>1.86</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>900</v>
+        <v>872.85</v>
       </c>
       <c r="I76" t="n">
         <v>898.8690357009647</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K76" t="n">
-        <v>-8.74</v>
+        <v>-11.49</v>
       </c>
       <c r="L76" t="n">
-        <v>10.26</v>
+        <v>11.86</v>
       </c>
       <c r="M76" t="n">
         <v>0.96</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,12 @@
       <c r="Q77" t="n">
         <v>6</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7864,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7874,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7884,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7894,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7904,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7914,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.8</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7924,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7934,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7944,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7954,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.67</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.51</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7974,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.21</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7984,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.05</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7994,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8004,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.8</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8014,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.39</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8024,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.04</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8034,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8044,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8054,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -7135,7 +8064,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.45</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="26">
@@ -7145,7 +8074,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.67</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8084,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.48</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8094,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
